--- a/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
@@ -771,67 +771,67 @@
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
+      <color rgb="FF183C1B"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -839,72 +839,72 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="16"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -1173,7 +1173,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1197,7 +1197,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1221,7 +1221,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1245,7 +1245,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1269,7 +1269,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1293,7 +1293,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1317,7 +1317,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1341,7 +1341,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1365,7 +1365,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1389,7 +1389,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1413,7 +1413,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1437,7 +1437,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1461,7 +1461,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1485,7 +1485,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1509,7 +1509,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1533,7 +1533,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1557,7 +1557,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1581,7 +1581,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1605,7 +1605,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1629,7 +1629,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1653,7 +1653,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1677,7 +1677,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1701,7 +1701,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1725,7 +1725,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1749,7 +1749,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1773,7 +1773,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1797,7 +1797,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1821,7 +1821,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1845,7 +1845,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1869,7 +1869,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1893,7 +1893,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1917,7 +1917,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1941,7 +1941,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1965,7 +1965,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -1989,7 +1989,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -2013,7 +2013,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -2037,7 +2037,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -3041,8 +3041,8 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
@@ -3064,7 +3064,7 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
         <a:font script="Armn" typeface="Arial"/>
@@ -3341,7 +3341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEA2BE2-6618-4872-A066-84342C0AF67F}">
   <dimension ref="B3:D16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28.25" customWidth="1"/>
     <col min="2" max="2" width="41.75" style="1" customWidth="1"/>
@@ -3350,7 +3350,8 @@
     <col min="5" max="5" width="30.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1"/>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>-33.8688</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -3366,7 +3367,7 @@
         <v>151.20930000000001</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>43831</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -3382,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
@@ -3398,7 +3399,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
@@ -3407,12 +3408,12 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" ht="20" x14ac:dyDescent="0.3" customHeight="1">
       <c r="B14" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3446,7 +3447,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.875" style="10" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="10" customWidth="1"/>
@@ -3460,13 +3461,13 @@
     <col min="15" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="23" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="9" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
       <c r="E3" s="24"/>
@@ -3479,7 +3480,7 @@
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="25" t="s">
         <v>80</v>
       </c>
@@ -3502,7 +3503,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="26" t="s">
         <v>87</v>
       </c>
@@ -3547,7 +3548,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.875" style="11" customWidth="1"/>
     <col min="2" max="2" width="2.375" style="11" customWidth="1"/>
@@ -3580,10 +3581,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -3610,11 +3611,11 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="BM4" s="14"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
       <c r="D5" s="16" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -3622,7 +3623,7 @@
       </c>
       <c r="BM5" s="14"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>91</v>
       </c>
@@ -3636,7 +3637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -3654,7 +3655,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -3672,7 +3673,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="D9" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -3687,7 +3688,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="D10" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -3702,7 +3703,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="D11" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -3718,7 +3719,7 @@
       </c>
       <c r="BM11" s="14"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="D12" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -3734,7 +3735,7 @@
       </c>
       <c r="BM12" s="14"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="D13" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -3749,7 +3750,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="D14" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -3764,129 +3765,129 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="D18" s="16" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="D20" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="D21" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D21" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="D22" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D22" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="D23" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="D24" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D24" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="D25" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="D26" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D26" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="D27" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D27" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="D28" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="D29" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="D30" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D30" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="D34" s="16" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="D36" s="17" t="s">
         <v>18</v>
@@ -3895,7 +3896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="D37" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D37" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3906,7 +3907,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="D38" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D38" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3917,7 +3918,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="D39" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D39" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3928,7 +3929,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
       <c r="D40" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D40" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3939,7 +3940,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="D41" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D41" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3950,7 +3951,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="D42" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3961,7 +3962,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="D43" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -3972,24 +3973,24 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="D45" s="16" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
       <c r="D47" s="17" t="s">
         <v>18</v>
@@ -4007,7 +4008,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
       <c r="D48" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4030,7 +4031,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
       <c r="D49" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4053,7 +4054,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
       <c r="D50" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4076,7 +4077,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
       <c r="D51" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4099,7 +4100,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
       <c r="D52" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4122,7 +4123,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
       <c r="D53" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4145,7 +4146,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
       <c r="D54" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -4168,49 +4169,49 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10"/>
       <c r="D57" s="16" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10"/>
       <c r="D59" s="19" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10"/>
       <c r="D60" s="19" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10"/>
       <c r="D61" s="19" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10"/>
       <c r="D63" s="17" t="s">
         <v>24</v>
@@ -4219,7 +4220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
       <c r="D64" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4230,7 +4231,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
       <c r="D65" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D65" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4241,7 +4242,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
       <c r="D66" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D66" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4252,7 +4253,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10"/>
       <c r="D67" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4263,7 +4264,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10"/>
       <c r="D68" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D68" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4274,7 +4275,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="D69" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4285,7 +4286,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="10"/>
       <c r="D70" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4296,7 +4297,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="D71" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4307,7 +4308,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10"/>
       <c r="D72" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4318,7 +4319,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10"/>
       <c r="D73" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D73" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4329,7 +4330,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10"/>
       <c r="D74" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D74" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4340,7 +4341,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10"/>
       <c r="D75" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D75" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4351,7 +4352,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10"/>
       <c r="D76" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D76" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4362,7 +4363,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10"/>
       <c r="D77" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D77" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -4373,64 +4374,64 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="10"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10"/>
       <c r="D81" s="16" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10"/>
       <c r="D83" s="19" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10"/>
       <c r="D84" s="19" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10"/>
       <c r="D85" s="19" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10"/>
       <c r="D86" s="19" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10"/>
       <c r="D87" s="19" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10"/>
       <c r="D89" s="17" t="s">
         <v>24</v>
@@ -4482,7 +4483,7 @@
       </c>
       <c r="T89" s="17"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="10"/>
       <c r="D90" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4550,7 +4551,7 @@
       </c>
       <c r="T90" s="17"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="10"/>
       <c r="D91" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4618,7 +4619,7 @@
       </c>
       <c r="T91" s="17"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="10"/>
       <c r="D92" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4686,7 +4687,7 @@
       </c>
       <c r="T92" s="17"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="10"/>
       <c r="D93" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4754,7 +4755,7 @@
       </c>
       <c r="T93" s="17"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="10"/>
       <c r="D94" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4822,7 +4823,7 @@
       </c>
       <c r="T94" s="17"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="10"/>
       <c r="D95" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4890,7 +4891,7 @@
       </c>
       <c r="T95" s="17"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="10"/>
       <c r="D96" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -4958,7 +4959,7 @@
       </c>
       <c r="T96" s="17"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="10"/>
       <c r="D97" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -5026,66 +5027,66 @@
       </c>
       <c r="T97" s="17"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="10"/>
       <c r="D99" s="20" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="10"/>
       <c r="D100" s="20" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="10"/>
       <c r="D101" s="20" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="10"/>
       <c r="D102" s="20" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="10"/>
       <c r="D103" s="20"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="10"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="10"/>
       <c r="D105" s="16" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="10"/>
       <c r="D107" s="19" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="10"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="10"/>
       <c r="D109" s="17" t="s">
         <v>41</v>
@@ -5100,7 +5101,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="10"/>
       <c r="D110" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -5119,7 +5120,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="10"/>
       <c r="D111" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -5138,7 +5139,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10"/>
       <c r="D112" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -5157,13 +5158,13 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="10"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="10"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10"/>
       <c r="D115" s="16" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -5171,7 +5172,7 @@
       </c>
       <c r="BN115" s="11"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="10"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -5179,7 +5180,7 @@
       </c>
       <c r="BN116" s="11"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="10"/>
       <c r="D117" s="19" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -5187,11 +5188,11 @@
       </c>
       <c r="BN117" s="11"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="10"/>
       <c r="BN118" s="11"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10"/>
       <c r="D119" s="17" t="s">
         <v>44</v>
@@ -5207,7 +5208,7 @@
       </c>
       <c r="BN119" s="11"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="10"/>
       <c r="D120" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -5227,7 +5228,7 @@
       </c>
       <c r="BN120" s="11"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="D121" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -5247,31 +5248,31 @@
       </c>
       <c r="BN121" s="11"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="BN122" s="11"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="10"/>
       <c r="D124" s="16" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="10"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="10"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="10"/>
       <c r="D127" s="17" t="s">
         <v>46</v>
@@ -5280,7 +5281,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="10"/>
       <c r="D128" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D128" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -5291,7 +5292,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="10"/>
       <c r="D129" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D129" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -5302,13 +5303,13 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="10"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="10"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="10"/>
       <c r="D132" s="16" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -5316,7 +5317,7 @@
       </c>
       <c r="E132" s="21"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="10"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -5324,7 +5325,7 @@
       </c>
       <c r="E133" s="21"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="10"/>
       <c r="D134" s="10" t="s">
         <v>48</v>
@@ -5333,7 +5334,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="10"/>
       <c r="D135" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="D135" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -5344,7 +5345,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="10"/>
       <c r="D136" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D136" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -5355,10 +5356,10 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="10"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="10"/>
       <c r="BN138" s="11"/>
       <c r="BO138" s="11"/>
@@ -5373,7 +5374,7 @@
       <c r="BX138" s="11"/>
       <c r="BY138" s="11"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="10"/>
       <c r="D139" s="16" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -5392,7 +5393,7 @@
       <c r="BX139" s="11"/>
       <c r="BY139" s="11"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="10"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -5411,7 +5412,7 @@
       <c r="BX140" s="11"/>
       <c r="BY140" s="11"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="10"/>
       <c r="D141" s="19" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -5419,7 +5420,7 @@
       </c>
       <c r="BN141" s="11"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="10"/>
       <c r="D142" s="17" t="s">
         <v>50</v>
@@ -5429,7 +5430,7 @@
       </c>
       <c r="BN142" s="11"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="10"/>
       <c r="D143" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D143" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -5441,7 +5442,7 @@
       </c>
       <c r="BN143" s="11"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="10"/>
       <c r="D144" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D144" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -5453,7 +5454,7 @@
       </c>
       <c r="BN144" s="11"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="10"/>
       <c r="D145" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D145" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -5465,7 +5466,7 @@
       </c>
       <c r="BN145" s="11"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="10"/>
       <c r="D146" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D146" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -5477,7 +5478,7 @@
       </c>
       <c r="BN146" s="11"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="10"/>
       <c r="D147" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D147" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -5489,15 +5490,15 @@
       </c>
       <c r="BN147" s="11"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="10"/>
       <c r="BN148" s="11"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="10"/>
       <c r="BN149" s="11"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="10"/>
       <c r="D150" s="16" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -5505,7 +5506,7 @@
       </c>
       <c r="BN150" s="11"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="10"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -5513,11 +5514,11 @@
       </c>
       <c r="BN151" s="11"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="10"/>
       <c r="BN152" s="11"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="10"/>
       <c r="D153" s="17" t="s">
         <v>51</v>
@@ -5537,7 +5538,7 @@
       <c r="BL153" s="14"/>
       <c r="BM153" s="14"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="10"/>
       <c r="D154" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D154" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -5559,7 +5560,7 @@
       <c r="BL154" s="14"/>
       <c r="BM154" s="14"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="10"/>
       <c r="D155" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D155" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -5581,7 +5582,7 @@
       <c r="BL155" s="14"/>
       <c r="BM155" s="14"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="10"/>
       <c r="D156" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D156" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -5592,7 +5593,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="10"/>
       <c r="D157" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D157" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -5603,7 +5604,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="10"/>
       <c r="D158" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D158" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -5614,34 +5615,34 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="10"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="10"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="16" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="21"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="21"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="21"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="21" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -5650,17 +5651,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="11"/>
       <c r="BO165" s="11"/>
       <c r="BP165" s="11"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="11"/>
       <c r="BO166" s="11"/>
       <c r="BP166" s="11"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="16" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -5669,7 +5670,7 @@
       <c r="BO167" s="11"/>
       <c r="BP167" s="11"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -5678,7 +5679,7 @@
       <c r="BO168" s="11"/>
       <c r="BP168" s="11"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -5687,7 +5688,7 @@
       <c r="BO169" s="11"/>
       <c r="BP169" s="11"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="15" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -5699,17 +5700,17 @@
       <c r="BO170" s="11"/>
       <c r="BP170" s="11"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="11"/>
       <c r="BO171" s="11"/>
       <c r="BP171" s="11"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="11"/>
       <c r="BO172" s="11"/>
       <c r="BP172" s="11"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="16" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -5718,7 +5719,7 @@
       <c r="BO173" s="11"/>
       <c r="BP173" s="11"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -5727,7 +5728,7 @@
       <c r="BO174" s="11"/>
       <c r="BP174" s="11"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="15" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -5740,17 +5741,17 @@
       <c r="BO175" s="11"/>
       <c r="BP175" s="11"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="11"/>
       <c r="BO176" s="11"/>
       <c r="BP176" s="11"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="11"/>
       <c r="BO177" s="11"/>
       <c r="BP177" s="11"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="16" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -5759,7 +5760,7 @@
       <c r="BO178" s="11"/>
       <c r="BP178" s="11"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -5768,39 +5769,39 @@
       <c r="BO179" s="11"/>
       <c r="BP179" s="11"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="20" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="19" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="19" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="19" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="19" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="19" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="17" t="s">
         <v>53</v>
       </c>
@@ -5817,7 +5818,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5839,7 +5840,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5861,7 +5862,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5883,7 +5884,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5905,7 +5906,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5927,7 +5928,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5949,7 +5950,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5971,7 +5972,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -5993,7 +5994,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -6015,7 +6016,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -6037,7 +6038,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -6059,7 +6060,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -6081,7 +6082,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v/>
@@ -6103,31 +6104,31 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="16" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="19" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="20" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="17" t="s">
         <v>24</v>
       </c>
@@ -6135,7 +6136,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D207" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v/>
@@ -6145,7 +6146,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D208" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v/>
@@ -6155,13 +6156,13 @@
         <v/>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="15" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="17" t="s">
         <v>59</v>
       </c>
@@ -6169,7 +6170,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D213" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6179,7 +6180,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D214" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6189,7 +6190,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D215" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6199,7 +6200,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D216" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6209,7 +6210,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D217" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6219,7 +6220,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D218" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6229,7 +6230,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D219" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6239,7 +6240,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D220" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6249,7 +6250,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D221" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6259,7 +6260,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D222" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6269,7 +6270,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D223" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6279,7 +6280,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D224" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v/>
@@ -6289,25 +6290,25 @@
         <v/>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="16" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="19" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="17" t="s">
         <v>61</v>
       </c>
@@ -6357,7 +6358,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6423,7 +6424,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6489,7 +6490,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6555,7 +6556,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6621,7 +6622,7 @@
         <v/>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6687,7 +6688,7 @@
         <v/>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6753,7 +6754,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6819,7 +6820,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6885,7 +6886,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -6951,7 +6952,7 @@
         <v/>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7017,7 +7018,7 @@
         <v/>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7083,7 +7084,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7149,7 +7150,7 @@
         <v/>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7215,7 +7216,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7281,7 +7282,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7347,7 +7348,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7413,7 +7414,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7479,7 +7480,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7545,7 +7546,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v/>
@@ -7611,31 +7612,31 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="16" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="15" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="20" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="17" t="s">
         <v>77</v>
       </c>
@@ -7643,7 +7644,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="D258" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v/>
@@ -7653,7 +7654,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="15" t="str" cm="1">
         <f t="array" aca="1" ref="D259" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v/>
@@ -7663,17 +7664,17 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="17" t="s">
         <v>94</v>
       </c>
@@ -7684,7 +7685,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="17" t="s">
         <v>96</v>
       </c>
@@ -7695,7 +7696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="17" t="s">
         <v>98</v>
       </c>
@@ -7706,7 +7707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="17" t="s">
         <v>99</v>
       </c>
@@ -7717,7 +7718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="17" t="s">
         <v>101</v>
       </c>
@@ -7728,7 +7729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="17" t="s">
         <v>103</v>
       </c>
@@ -7739,12 +7740,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="17" t="s">
         <v>94</v>
       </c>
@@ -7755,7 +7756,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="17" t="s">
         <v>106</v>
       </c>
@@ -7766,7 +7767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="17" t="s">
         <v>107</v>
       </c>
@@ -7777,7 +7778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="17" t="s">
         <v>109</v>
       </c>
@@ -7788,7 +7789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="17" t="s">
         <v>111</v>
       </c>
@@ -7799,7 +7800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="17" t="s">
         <v>113</v>
       </c>
@@ -7810,12 +7811,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="17" t="s">
         <v>94</v>
       </c>
@@ -7826,7 +7827,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="17" t="s">
         <v>116</v>
       </c>
@@ -7837,7 +7838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="17" t="s">
         <v>118</v>
       </c>
@@ -7848,7 +7849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="17" t="s">
         <v>120</v>
       </c>
@@ -7859,7 +7860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="17" t="s">
         <v>121</v>
       </c>
@@ -7870,7 +7871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="17" t="s">
         <v>123</v>
       </c>
@@ -7881,12 +7882,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="17" t="s">
         <v>94</v>
       </c>
@@ -7897,7 +7898,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="17" t="s">
         <v>126</v>
       </c>
@@ -7908,7 +7909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="17" t="s">
         <v>128</v>
       </c>
@@ -7919,7 +7920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="17" t="s">
         <v>130</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="17" t="s">
         <v>132</v>
       </c>
@@ -7941,7 +7942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="17" t="s">
         <v>134</v>
       </c>
